--- a/Requetes.xlsx
+++ b/Requetes.xlsx
@@ -1,48 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\103354706\Box Sync\00 - Bob\Festival\FESTIVAL (WORK IN PROGRESS)\Rapports\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8FE661F-52A2-4C47-AF2A-6CFFF358EC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{698E7B4A-C039-4E60-9939-5720CAAB4279}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Requetes" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Requetes" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Requetes!$A$1:$D$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
@@ -59,31 +28,108 @@
     <t>30/07/2026</t>
   </si>
   <si>
+    <t>14:57</t>
+  </si>
+  <si>
     <t>Peux tu me créer un fichier excel qui liste les requetes demandées ? Je veux dans le fichier les colonnes suivantes : Date, Heure, Requete (texte saisi dans BOB), Reponse Bob : un résumé de la réponse de Bob. Je veux que ce fichier excel soit alimenté après chaque demande et stocker dans le fichier RAPPORTS sous le nom 'Requete'</t>
   </si>
   <si>
     <t>Création du fichier Requetes.xlsx dans Rapports/ avec les colonnes Date/Heure/Requete/Reponse Bob. Ajout d'un endpoint POST /log-requete dans server.js pour logger automatiquement chaque échange. Correction du bug écran détail Rapport_Informations_Ateliers.html (display:none).</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>Dans « Charge de travail — Helpers, Angels &amp; Traducteurs », lors de l'affichage des infos d'une personne, afficher les différents rôles de façon distincte et non pas « Helper + Traducteur ». Appliquer la même logique que pour l'affichage par jours. Retirer l'émojicône devant chaque rôle.</t>
+  </si>
+  <si>
+    <t>Rapport_Charge_Travail.html : dans renderPersonCard, le badge de rôle du header est maintenant décomposé en badges distincts (badge-h, badge-a, badge-t) en splittant sur ' + '. Suppression des émojis 🤝 👼 🌐 devant Helper, Angel, Traducteur dans les blocs d'ateliers, les blocs shift angel, et les badges de jour.</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>Dans « Charge de travail — Helpers, Angels &amp; Traducteurs », si un shift angel, comptabiliser 1 seul atelier. Ne pas comptabiliser les ateliers qui ont lieu au même moment.</t>
+  </si>
+  <si>
+    <t>Rapport_Charge_Travail.html : le compteur nbJour du label de chaque jour utilise désormais merged.length (blocs temporels fusionnés après interval merging) pour les vues Angel/Traducteur pures, et filtre les ateliers couverts par un créneau plus long en vue combinée. Cohérence avec person.count déjà calculé via uniqueSlots.</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>Dans « Charge de travail — Helpers, Angels &amp; Traducteurs », utiliser les mêmes codes couleur que dans le rapport « Mon Planning V2 » : couleur de la ligne nom, puis jour et atelier.</t>
+  </si>
+  <si>
+    <t>Rapport_Charge_Travail.html : --header-bg:#1e40af / --header-tx:#ffffff pour la ligne NOM (bleu foncé, texte blanc), --day-bg:#374151 / --day-tx:#f9fafb pour la ligne JOUR (gris foncé). Adaptation du rang, des stats, de la barre de charge, du chevron et du hover sur fond coloré. Mode nuit : --header-bg:#1e3a8a, --day-bg:#1f2937.</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>Dans « Charge de travail — Helpers, Angels &amp; Traducteurs », assurer que le rapport est correctement traduit : nom du rapport, champs, onglets, summaryBar, messages, section harmonisation.</t>
+  </si>
+  <si>
+    <t>ref_translations.js : 90+ nouvelles clés r6_* ajoutées (sous-titre, onglets, filtres, summary bar, carte personne, messages vides, navigation harmonisation, textes d'intro, tous titres et corps des cartes). Rapport_Charge_Travail.html : intégralité des textes hardcodés remplacés par I18n.t() dans le HTML statique et le JS dynamique (renderPersonCard, buildHarmony, render, renderHarmony, toggleMode). HARMONY_INTROS remplacé par getHarmonyIntros() pour réévaluation dynamique.</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>Dans « My Schedule V2 », si un shift angel, d'abord afficher uniquement le shift angel, et au clic afficher le détail des ateliers concernés.</t>
+  </si>
+  <si>
+    <t>Rapport_Mon_Planning_V2.html : les lignes angel-covered-row sont masquées par défaut (display:none). Le shift angel reçoit data-shift-group, les ateliers couverts data-shift-member. Clic sur le shift → toggleAngelShift() bascule la classe shift-visible sur les membres et fait pivoter le chevron › intégré. Compteur '3 ateliers' affiché dans la pill du shift.</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>Dans « Programme », si l'on passe en MODE NUIT, on n'arrive pas à lire les badges ENG/FR et les notes. Changer la couleur de la police en noir.</t>
+  </si>
+  <si>
+    <t>Rapport_Programme.html : ajout de .dark .prog-main .badge-note, .dark .prog-main .badge-trad { color:#111111 !important; }. Les sélecteurs .dark .type-section.section-* .prog-main * avaient une spécificité plus haute et forçaient color:#f9fafb sur tous les descendants.</t>
+  </si>
+  <si>
+    <t>16/07/2026</t>
+  </si>
+  <si>
+    <t>Dans INDEX BIS et GESTION PLANNING, changer la couleur de la box du rapport « Mon Planning V2 » en un jaune clair.</t>
+  </si>
+  <si>
+    <t>index_bis.html et gestion_planning.html : background #90ee90 (vert) remplacé par #fef9c3 (jaune clair) avec border-color #fde68a.</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>Alimenter le fichier « REQUETES » avec les requêtes faites sur les 2 dernières semaines.</t>
+  </si>
+  <si>
+    <t>Requetes.xlsx mis à jour avec les 7 nouvelles requêtes de la conversation (14-16 juillet 2026) via script ExcelJS. Colonnes : Date, Heure, Requete, Reponse Bob.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -95,8 +141,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4823B"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF1E40AF"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,15 +157,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -150,44 +193,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -215,31 +258,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -267,23 +293,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -295,136 +304,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -446,54 +499,162 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7174D0AF-4D3D-4782-89BA-F89FDEB1F101}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" customWidth="1"/>
-    <col min="3" max="4" width="60.77734375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
+    <col min="4" max="4" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.62291666666666667</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{7174D0AF-4D3D-4782-89BA-F89FDEB1F101}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>